--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_020726.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_020726.xlsx
@@ -8,23 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43837DBB-E6D6-4F22-9020-39AAF8F52D88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAA493B-5776-4A45-B801-AEAA42B9DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
     <sheet name="ID_VNSH03" sheetId="12" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">NhapKho_SX!$A$1:$M$20</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">NhapKho_SX!$A$1:$M$21</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="42">
   <si>
     <t>STT</t>
   </si>
@@ -69,12 +69,6 @@
 </t>
   </si>
   <si>
-    <t>Phòngban/ Bộ phận: PKT/ Bảo hành - Sản xuất…..</t>
-  </si>
-  <si>
-    <t>Tên Khách hàng:…...............................................</t>
-  </si>
-  <si>
     <t>Công Ty Cổ Phần Công Nghệ Điện Tử &amp; Viễn  Thông Việt Nam</t>
   </si>
   <si>
@@ -155,6 +149,9 @@
   </si>
   <si>
     <t>VNET861385071516432</t>
+  </si>
+  <si>
+    <t>Phòngban/ Bộ phận: PKT/ Bảo hành - Sản xuất</t>
   </si>
 </sst>
 </file>
@@ -477,7 +474,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -655,11 +652,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -687,13 +681,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>488016</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>164224</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>307039</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>164224</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1072,7 +1066,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N33"/>
+  <dimension ref="A1:N34"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" customWidth="1"/>
@@ -1094,7 +1088,7 @@
       <c r="B1" s="46"/>
       <c r="C1" s="47"/>
       <c r="D1" s="54" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E1" s="55"/>
       <c r="F1" s="55"/>
@@ -1106,7 +1100,7 @@
       <c r="B2" s="49"/>
       <c r="C2" s="50"/>
       <c r="D2" s="57" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E2" s="57"/>
       <c r="F2" s="57"/>
@@ -1118,7 +1112,7 @@
       <c r="B3" s="49"/>
       <c r="C3" s="50"/>
       <c r="D3" s="57" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E3" s="57"/>
       <c r="F3" s="57"/>
@@ -1130,7 +1124,7 @@
       <c r="B4" s="52"/>
       <c r="C4" s="53"/>
       <c r="D4" s="59" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E4" s="59"/>
       <c r="F4" s="59"/>
@@ -1139,7 +1133,7 @@
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="42" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B5" s="43"/>
       <c r="C5" s="43"/>
@@ -1149,155 +1143,153 @@
       <c r="G5" s="43"/>
       <c r="H5" s="44"/>
     </row>
-    <row r="6" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="8"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="14" t="s">
-        <v>30</v>
-      </c>
+    <row r="6" spans="1:8" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="61"/>
+      <c r="D6" s="61"/>
+      <c r="E6" s="61"/>
+      <c r="F6" s="61"/>
+      <c r="G6" s="61"/>
+      <c r="H6" s="61"/>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="9"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="14"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="14" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="8" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="9"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-    </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:8" s="4" customFormat="1" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="8"/>
+      <c r="B9" s="8"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B10" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C10" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="22" t="s">
+      <c r="D10" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F10" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="33">
+      <c r="G10" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="2" customFormat="1" ht="25.5" x14ac:dyDescent="0.2">
+      <c r="A11" s="33">
         <v>1</v>
       </c>
-      <c r="B10" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" s="33" t="s">
+      <c r="B11" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="34">
+      <c r="C11" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="34">
         <v>12</v>
       </c>
-      <c r="E10" s="33"/>
-      <c r="F10" s="33"/>
-      <c r="G10" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="H10" s="35"/>
-    </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="11"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="11"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="35" t="s">
+        <v>24</v>
+      </c>
+      <c r="H11" s="35"/>
     </row>
     <row r="12" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="13"/>
+      <c r="A12" s="10"/>
+      <c r="B12" s="10"/>
       <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="11"/>
     </row>
     <row r="13" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="16" t="s">
-        <v>20</v>
-      </c>
+      <c r="A13" s="13"/>
       <c r="B13" s="13"/>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="3"/>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3"/>
+      <c r="F13" s="3"/>
+      <c r="G13" s="3"/>
+      <c r="H13" s="3"/>
+    </row>
+    <row r="14" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="18" t="s">
+      <c r="D14" s="3"/>
+      <c r="E14" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="20" t="s">
+      <c r="F14" s="13"/>
+      <c r="G14" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="H13" s="13"/>
-    </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="25" t="s">
+      <c r="H14" s="13"/>
+    </row>
+    <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="27" t="s">
+      <c r="B15" s="26"/>
+      <c r="C15" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="D14" s="28"/>
-      <c r="E14" s="29" t="s">
+      <c r="D15" s="28"/>
+      <c r="E15" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="F14" s="26"/>
-      <c r="G14" s="30" t="s">
+      <c r="F15" s="26"/>
+      <c r="G15" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="H14" s="26"/>
-    </row>
-    <row r="15" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="26"/>
     </row>
     <row r="16" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13"/>
@@ -1313,8 +1305,8 @@
       <c r="A17" s="13"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="D17" s="13"/>
+      <c r="E17" s="13"/>
       <c r="F17" s="13"/>
       <c r="G17" s="21"/>
       <c r="H17" s="13"/>
@@ -1323,10 +1315,10 @@
       <c r="A18" s="13"/>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
       <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
+      <c r="G18" s="21"/>
       <c r="H18" s="13"/>
     </row>
     <row r="19" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1336,48 +1328,58 @@
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
       <c r="F19" s="13"/>
-      <c r="G19" s="21"/>
+      <c r="G19" s="13"/>
       <c r="H19" s="13"/>
     </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="13"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="13"/>
+    </row>
+    <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="13"/>
-      <c r="C20" s="18" t="s">
+      <c r="B21" s="13"/>
+      <c r="C21" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="17" t="s">
+      <c r="D21" s="3"/>
+      <c r="E21" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="18" t="s">
+      <c r="F21" s="13"/>
+      <c r="G21" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="H20" s="13"/>
-    </row>
-    <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="F22" s="32"/>
-      <c r="G22" s="32"/>
-      <c r="H22" s="32"/>
-    </row>
-    <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="H21" s="13"/>
+    </row>
+    <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="23" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="F23" s="32"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="32"/>
+    </row>
     <row r="24" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="25" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:8" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-    </row>
-    <row r="27" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="26" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="27" spans="1:8" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+    </row>
     <row r="28" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="8:8" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="H33" s="5"/>
+    <row r="29" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="8:8" ht="15.75" x14ac:dyDescent="0.2">
+      <c r="H34" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1408,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="39" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1416,7 +1418,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1424,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1432,7 +1434,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1440,7 +1442,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1448,7 +1450,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1456,7 +1458,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1464,7 +1466,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1472,7 +1474,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1480,7 +1482,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1488,7 +1490,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1496,7 +1498,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="15" x14ac:dyDescent="0.2">
@@ -1504,120 +1506,120 @@
         <v>12</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A14" s="61"/>
-      <c r="B14" s="62"/>
+      <c r="A14" s="38"/>
+      <c r="B14" s="41"/>
     </row>
     <row r="15" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A15" s="61"/>
-      <c r="B15" s="62"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="41"/>
     </row>
     <row r="16" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A16" s="61"/>
-      <c r="B16" s="62"/>
+      <c r="A16" s="38"/>
+      <c r="B16" s="41"/>
     </row>
     <row r="17" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A17" s="61"/>
-      <c r="B17" s="62"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="41"/>
     </row>
     <row r="18" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A18" s="61"/>
-      <c r="B18" s="62"/>
+      <c r="A18" s="38"/>
+      <c r="B18" s="41"/>
     </row>
     <row r="19" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A19" s="61"/>
-      <c r="B19" s="62"/>
+      <c r="A19" s="38"/>
+      <c r="B19" s="41"/>
     </row>
     <row r="20" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A20" s="61"/>
-      <c r="B20" s="62"/>
+      <c r="A20" s="38"/>
+      <c r="B20" s="41"/>
     </row>
     <row r="21" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A21" s="61"/>
-      <c r="B21" s="62"/>
+      <c r="A21" s="38"/>
+      <c r="B21" s="41"/>
     </row>
     <row r="22" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A22" s="61"/>
-      <c r="B22" s="62"/>
+      <c r="A22" s="38"/>
+      <c r="B22" s="41"/>
     </row>
     <row r="23" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A23" s="61"/>
-      <c r="B23" s="62"/>
+      <c r="A23" s="38"/>
+      <c r="B23" s="41"/>
     </row>
     <row r="24" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A24" s="61"/>
-      <c r="B24" s="62"/>
+      <c r="A24" s="38"/>
+      <c r="B24" s="41"/>
     </row>
     <row r="25" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A25" s="61"/>
-      <c r="B25" s="62"/>
+      <c r="A25" s="38"/>
+      <c r="B25" s="41"/>
     </row>
     <row r="26" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A26" s="61"/>
-      <c r="B26" s="62"/>
+      <c r="A26" s="38"/>
+      <c r="B26" s="41"/>
     </row>
     <row r="27" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A27" s="61"/>
-      <c r="B27" s="62"/>
+      <c r="A27" s="38"/>
+      <c r="B27" s="41"/>
     </row>
     <row r="28" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="61"/>
-      <c r="B28" s="62"/>
+      <c r="A28" s="38"/>
+      <c r="B28" s="41"/>
     </row>
     <row r="29" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A29" s="61"/>
-      <c r="B29" s="62"/>
+      <c r="A29" s="38"/>
+      <c r="B29" s="41"/>
     </row>
     <row r="30" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="61"/>
-      <c r="B30" s="62"/>
+      <c r="A30" s="38"/>
+      <c r="B30" s="41"/>
     </row>
     <row r="31" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A31" s="61"/>
-      <c r="B31" s="62"/>
+      <c r="A31" s="38"/>
+      <c r="B31" s="41"/>
     </row>
     <row r="32" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A32" s="61"/>
-      <c r="B32" s="62"/>
+      <c r="A32" s="38"/>
+      <c r="B32" s="41"/>
     </row>
     <row r="33" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A33" s="61"/>
-      <c r="B33" s="62"/>
+      <c r="A33" s="38"/>
+      <c r="B33" s="41"/>
     </row>
     <row r="34" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A34" s="61"/>
-      <c r="B34" s="62"/>
+      <c r="A34" s="38"/>
+      <c r="B34" s="41"/>
     </row>
     <row r="35" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A35" s="61"/>
-      <c r="B35" s="62"/>
+      <c r="A35" s="38"/>
+      <c r="B35" s="41"/>
     </row>
     <row r="36" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A36" s="61"/>
-      <c r="B36" s="62"/>
+      <c r="A36" s="38"/>
+      <c r="B36" s="41"/>
     </row>
     <row r="37" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A37" s="61"/>
-      <c r="B37" s="62"/>
+      <c r="A37" s="38"/>
+      <c r="B37" s="41"/>
     </row>
     <row r="38" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A38" s="61"/>
-      <c r="B38" s="62"/>
+      <c r="A38" s="38"/>
+      <c r="B38" s="41"/>
     </row>
     <row r="39" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A39" s="61"/>
-      <c r="B39" s="62"/>
+      <c r="A39" s="38"/>
+      <c r="B39" s="41"/>
     </row>
     <row r="40" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A40" s="61"/>
-      <c r="B40" s="62"/>
+      <c r="A40" s="38"/>
+      <c r="B40" s="41"/>
     </row>
     <row r="41" spans="1:2" ht="15" x14ac:dyDescent="0.2">
-      <c r="A41" s="61"/>
-      <c r="B41" s="62"/>
+      <c r="A41" s="38"/>
+      <c r="B41" s="41"/>
     </row>
     <row r="42" spans="1:2" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="38"/>

--- a/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_020726.xlsx
+++ b/2. Báo cáo - giấy tờ/3. Sản xuất/Xuất Nhập Kho 2026/Nhập kho/Tháng 07/NKSX_VNSH03_020726.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VNET\2. Báo cáo - giấy tờ\3. Sản xuất\Xuất Nhập Kho 2026\Nhập kho\Tháng 07\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EAA493B-5776-4A45-B801-AEAA42B9DD47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89E735D0-85F1-4477-87A8-65C1D301C893}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NhapKho_SX" sheetId="10" r:id="rId1"/>
@@ -595,6 +595,9 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -651,9 +654,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1082,76 +1082,76 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="46" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="46"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="54" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="55"/>
-      <c r="H1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="57"/>
     </row>
     <row r="2" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="48"/>
-      <c r="B2" s="49"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="57" t="s">
+      <c r="A2" s="49"/>
+      <c r="B2" s="50"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="58" t="s">
         <v>21</v>
       </c>
-      <c r="E2" s="57"/>
-      <c r="F2" s="57"/>
-      <c r="G2" s="57"/>
-      <c r="H2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="59"/>
     </row>
     <row r="3" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="48"/>
-      <c r="B3" s="49"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="57" t="s">
+      <c r="A3" s="49"/>
+      <c r="B3" s="50"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="57"/>
-      <c r="F3" s="57"/>
-      <c r="G3" s="57"/>
-      <c r="H3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="59"/>
     </row>
     <row r="4" spans="1:8" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="59" t="s">
+      <c r="A4" s="52"/>
+      <c r="B4" s="53"/>
+      <c r="C4" s="54"/>
+      <c r="D4" s="60" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="59"/>
-      <c r="F4" s="59"/>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60"/>
+      <c r="E4" s="60"/>
+      <c r="F4" s="60"/>
+      <c r="G4" s="60"/>
+      <c r="H4" s="61"/>
     </row>
     <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="42" t="s">
+      <c r="A5" s="43" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
-      <c r="E5" s="43"/>
-      <c r="F5" s="43"/>
-      <c r="G5" s="43"/>
-      <c r="H5" s="44"/>
+      <c r="B5" s="44"/>
+      <c r="C5" s="44"/>
+      <c r="D5" s="44"/>
+      <c r="E5" s="44"/>
+      <c r="F5" s="44"/>
+      <c r="G5" s="44"/>
+      <c r="H5" s="45"/>
     </row>
     <row r="6" spans="1:8" ht="5.0999999999999996" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
-      <c r="C6" s="61"/>
-      <c r="D6" s="61"/>
-      <c r="E6" s="61"/>
-      <c r="F6" s="61"/>
-      <c r="G6" s="61"/>
-      <c r="H6" s="61"/>
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="42"/>
+      <c r="D6" s="42"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
     </row>
     <row r="7" spans="1:8" s="4" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
